--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="139">
   <si>
     <t>Product Code</t>
   </si>
@@ -46,6 +46,9 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>Image File</t>
+  </si>
+  <si>
     <t>ABT-001</t>
   </si>
   <si>
@@ -163,6 +166,12 @@
     <t>ABT-039</t>
   </si>
   <si>
+    <t>ABT-040</t>
+  </si>
+  <si>
+    <t>ABT-041</t>
+  </si>
+  <si>
     <t>Soaps</t>
   </si>
   <si>
@@ -187,6 +196,12 @@
     <t>Miscellaneous</t>
   </si>
   <si>
+    <t>Checking</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
     <t>Turkish Soap</t>
   </si>
   <si>
@@ -238,7 +253,7 @@
     <t>Tissue Paper (Clean)</t>
   </si>
   <si>
-    <t>LaSafety Razor</t>
+    <t>Lady Safety Razor</t>
   </si>
   <si>
     <t>Sensitive Toothbrush</t>
@@ -283,7 +298,7 @@
     <t>Khansama (Gol)</t>
   </si>
   <si>
-    <t>USIRooyal Cards (Plastic)</t>
+    <t>USA Royal Cards (Plastic)</t>
   </si>
   <si>
     <t>Paradise Jaali (30g)</t>
@@ -304,6 +319,12 @@
     <t>Golden Cards</t>
   </si>
   <si>
+    <t>Card1</t>
+  </si>
+  <si>
+    <t>brought up</t>
+  </si>
+  <si>
     <t>Carton (48 pcs)</t>
   </si>
   <si>
@@ -367,7 +388,7 @@
     <t>Carton (576 pcs)</t>
   </si>
   <si>
-    <t>Carton (100 rolls x 12 pcs = 1200 pcs</t>
+    <t>Carton (100 rolls)</t>
   </si>
   <si>
     <t>Packet (24 pcs)</t>
@@ -379,6 +400,12 @@
     <t>Carton (6 boxes x 20 pcs = 120 pcs)</t>
   </si>
   <si>
+    <t>13 packets</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>Confirm pack size with supplier</t>
   </si>
   <si>
@@ -395,6 +422,15 @@
   </si>
   <si>
     <t>Price is per roll; each roll cuts into ~12 pieces</t>
+  </si>
+  <si>
+    <t>nice product</t>
+  </si>
+  <si>
+    <t>Card1.png</t>
+  </si>
+  <si>
+    <t>brought_up.png</t>
   </si>
 </sst>
 </file>
@@ -752,10 +788,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -786,19 +822,22 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -810,21 +849,24 @@
         <v>52.0833333333333</v>
       </c>
       <c r="H2">
-        <v>62.0833333333333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E3">
         <v>144</v>
@@ -836,21 +878,24 @@
         <v>7.63888888888889</v>
       </c>
       <c r="H3">
-        <v>17.6388888888889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -862,21 +907,24 @@
         <v>27.5</v>
       </c>
       <c r="H4">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -888,21 +936,24 @@
         <v>27.5</v>
       </c>
       <c r="H5">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -914,21 +965,24 @@
         <v>37.5</v>
       </c>
       <c r="H6">
-        <v>47.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -940,24 +994,27 @@
         <v>54.1666666666667</v>
       </c>
       <c r="H7">
-        <v>64.1666666666667</v>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -969,21 +1026,24 @@
         <v>15.8333333333333</v>
       </c>
       <c r="H8">
-        <v>25.8333333333333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -995,21 +1055,24 @@
         <v>11</v>
       </c>
       <c r="H9">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1021,24 +1084,27 @@
         <v>19.5</v>
       </c>
       <c r="H10">
-        <v>29.5</v>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -1050,21 +1116,24 @@
         <v>23.3333333333333</v>
       </c>
       <c r="H11">
-        <v>33.3333333333333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1076,21 +1145,24 @@
         <v>46.5</v>
       </c>
       <c r="H12">
-        <v>56.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E13">
         <v>384</v>
@@ -1102,21 +1174,24 @@
         <v>14.3229166666667</v>
       </c>
       <c r="H13">
-        <v>24.3229166666667</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -1128,24 +1203,27 @@
         <v>28.3333333333333</v>
       </c>
       <c r="H14">
-        <v>38.3333333333333</v>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1157,21 +1235,24 @@
         <v>30</v>
       </c>
       <c r="H15">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E16">
         <v>600</v>
@@ -1183,21 +1264,24 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -1209,21 +1293,24 @@
         <v>4.33333333333333</v>
       </c>
       <c r="H17">
-        <v>14.3333333333333</v>
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1235,24 +1322,27 @@
         <v>103.333333333333</v>
       </c>
       <c r="H18">
-        <v>113.333333333333</v>
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1264,21 +1354,24 @@
         <v>8.33333333333333</v>
       </c>
       <c r="H19">
-        <v>18.3333333333333</v>
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1290,21 +1383,24 @@
         <v>25</v>
       </c>
       <c r="H20">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -1316,21 +1412,24 @@
         <v>91.6666666666667</v>
       </c>
       <c r="H21">
-        <v>101.666666666667</v>
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1342,21 +1441,24 @@
         <v>76.6666666666667</v>
       </c>
       <c r="H22">
-        <v>86.6666666666667</v>
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1368,21 +1470,24 @@
         <v>83</v>
       </c>
       <c r="H23">
-        <v>93</v>
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -1394,21 +1499,24 @@
         <v>37.5</v>
       </c>
       <c r="H24">
-        <v>47.5</v>
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E25">
         <v>1000</v>
@@ -1420,21 +1528,24 @@
         <v>3.1</v>
       </c>
       <c r="H25">
-        <v>13.1</v>
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1446,24 +1557,27 @@
         <v>250</v>
       </c>
       <c r="H26">
-        <v>260</v>
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E27">
         <v>576</v>
@@ -1475,21 +1589,24 @@
         <v>8.680555555555561</v>
       </c>
       <c r="H27">
-        <v>18.6805555555556</v>
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E28">
         <v>576</v>
@@ -1501,21 +1618,24 @@
         <v>12.1527777777778</v>
       </c>
       <c r="H28">
-        <v>22.1527777777778</v>
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E29">
         <v>576</v>
@@ -1527,21 +1647,24 @@
         <v>5.20833333333333</v>
       </c>
       <c r="H29">
-        <v>15.2083333333333</v>
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E30">
         <v>576</v>
@@ -1553,21 +1676,24 @@
         <v>16.4930555555556</v>
       </c>
       <c r="H30">
-        <v>26.4930555555556</v>
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E31">
         <v>576</v>
@@ -1579,50 +1705,56 @@
         <v>11.2847222222222</v>
       </c>
       <c r="H31">
-        <v>21.2847222222222</v>
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E32">
-        <v>1200</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>4800</v>
       </c>
       <c r="G32">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="H32">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E33">
         <v>24</v>
@@ -1634,21 +1766,24 @@
         <v>8.75</v>
       </c>
       <c r="H33">
-        <v>18.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E34">
         <v>144</v>
@@ -1660,21 +1795,24 @@
         <v>131.944444444444</v>
       </c>
       <c r="H34">
-        <v>141.944444444444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -1686,21 +1824,24 @@
         <v>29.1666666666667</v>
       </c>
       <c r="H35">
-        <v>39.1666666666667</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -1712,21 +1853,24 @@
         <v>26.6666666666667</v>
       </c>
       <c r="H36">
-        <v>36.6666666666667</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -1738,21 +1882,24 @@
         <v>14.1666666666667</v>
       </c>
       <c r="H37">
-        <v>24.1666666666667</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -1764,21 +1911,24 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1790,21 +1940,24 @@
         <v>8.75</v>
       </c>
       <c r="H39">
-        <v>18.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -1816,7 +1969,77 @@
         <v>72.5</v>
       </c>
       <c r="H40">
-        <v>82.5</v>
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" t="s">
+        <v>101</v>
+      </c>
+      <c r="D41" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41">
+        <v>145</v>
+      </c>
+      <c r="F41">
+        <v>789</v>
+      </c>
+      <c r="G41">
+        <v>67</v>
+      </c>
+      <c r="H41">
+        <v>12</v>
+      </c>
+      <c r="I41">
+        <v>16</v>
+      </c>
+      <c r="J41" t="s">
+        <v>136</v>
+      </c>
+      <c r="K41" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
+      </c>
+      <c r="C42" t="s">
+        <v>102</v>
+      </c>
+      <c r="D42" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42">
+        <v>12</v>
+      </c>
+      <c r="F42">
+        <v>390</v>
+      </c>
+      <c r="G42">
+        <v>45</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="143">
   <si>
     <t>Product Code</t>
   </si>
@@ -199,7 +199,7 @@
     <t>Checking</t>
   </si>
   <si>
-    <t>Testing</t>
+    <t>soaps</t>
   </si>
   <si>
     <t>Turkish Soap</t>
@@ -322,10 +322,10 @@
     <t>Card1</t>
   </si>
   <si>
-    <t>brought up</t>
-  </si>
-  <si>
-    <t>Carton (48 pcs)</t>
+    <t>card2</t>
+  </si>
+  <si>
+    <t>Carton(48 pcs)</t>
   </si>
   <si>
     <t>Packet (144 pcs)</t>
@@ -397,16 +397,19 @@
     <t>Pack (144 pcs)</t>
   </si>
   <si>
+    <t>Dozen</t>
+  </si>
+  <si>
     <t>Carton (6 boxes x 20 pcs = 120 pcs)</t>
   </si>
   <si>
     <t>13 packets</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Confirm pack size with supplier</t>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Confirm pack size</t>
   </si>
   <si>
     <t>Supplier also quoted ~Rs 15/pc — confirm</t>
@@ -427,10 +430,19 @@
     <t>nice product</t>
   </si>
   <si>
+    <t>hi</t>
+  </si>
+  <si>
+    <t>Turkish_Soap.jpg</t>
+  </si>
+  <si>
+    <t>Toothpicks.png</t>
+  </si>
+  <si>
     <t>Card1.png</t>
   </si>
   <si>
-    <t>brought_up.png</t>
+    <t>card2.png</t>
   </si>
 </sst>
 </file>
@@ -849,10 +861,13 @@
         <v>52.0833333333333</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I2">
         <v>0</v>
+      </c>
+      <c r="K2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -872,7 +887,7 @@
         <v>144</v>
       </c>
       <c r="F3">
-        <v>1100</v>
+        <v>110</v>
       </c>
       <c r="G3">
         <v>7.63888888888889</v>
@@ -1000,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1031,6 +1046,9 @@
       <c r="I8">
         <v>0</v>
       </c>
+      <c r="K8" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
@@ -1090,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1209,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1328,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1563,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1740,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1928,7 +1946,7 @@
         <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1957,7 +1975,7 @@
         <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -1986,7 +2004,7 @@
         <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E41">
         <v>145</v>
@@ -2004,10 +2022,10 @@
         <v>16</v>
       </c>
       <c r="J41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K41" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2021,25 +2039,28 @@
         <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>12.86</v>
+      </c>
+      <c r="G42">
+        <v>56</v>
+      </c>
+      <c r="H42">
         <v>12</v>
       </c>
-      <c r="F42">
-        <v>390</v>
-      </c>
-      <c r="G42">
-        <v>45</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
       <c r="I42">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J42" t="s">
+        <v>138</v>
       </c>
       <c r="K42" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="150">
   <si>
     <t>Product Code</t>
   </si>
@@ -172,6 +172,12 @@
     <t>ABT-041</t>
   </si>
   <si>
+    <t>ABT-042</t>
+  </si>
+  <si>
+    <t>ABT-043</t>
+  </si>
+  <si>
     <t>Soaps</t>
   </si>
   <si>
@@ -202,6 +208,12 @@
     <t>soaps</t>
   </si>
   <si>
+    <t>Games</t>
+  </si>
+  <si>
+    <t>Pcard</t>
+  </si>
+  <si>
     <t>Turkish Soap</t>
   </si>
   <si>
@@ -325,6 +337,9 @@
     <t>card2</t>
   </si>
   <si>
+    <t>card3</t>
+  </si>
+  <si>
     <t>Carton(48 pcs)</t>
   </si>
   <si>
@@ -409,6 +424,9 @@
     <t>13</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>Confirm pack size</t>
   </si>
   <si>
@@ -443,6 +461,9 @@
   </si>
   <si>
     <t>card2.png</t>
+  </si>
+  <si>
+    <t>card3.png</t>
   </si>
 </sst>
 </file>
@@ -800,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -843,13 +864,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -858,7 +879,7 @@
         <v>2500</v>
       </c>
       <c r="G2">
-        <v>52.0833333333333</v>
+        <v>52.08</v>
       </c>
       <c r="H2">
         <v>20</v>
@@ -867,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -875,13 +896,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E3">
         <v>144</v>
@@ -890,7 +911,7 @@
         <v>110</v>
       </c>
       <c r="G3">
-        <v>7.63888888888889</v>
+        <v>0.76</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -904,13 +925,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -933,13 +954,13 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -962,13 +983,13 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -991,13 +1012,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -1006,7 +1027,7 @@
         <v>650</v>
       </c>
       <c r="G7">
-        <v>54.1666666666667</v>
+        <v>54.17</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1015,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1023,13 +1044,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1038,7 +1059,7 @@
         <v>190</v>
       </c>
       <c r="G8">
-        <v>15.8333333333333</v>
+        <v>15.83</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1047,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1055,13 +1076,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1084,13 +1105,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1108,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1116,13 +1137,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -1131,7 +1152,7 @@
         <v>280</v>
       </c>
       <c r="G11">
-        <v>23.3333333333333</v>
+        <v>23.33</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -1145,13 +1166,13 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1174,13 +1195,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E13">
         <v>384</v>
@@ -1189,7 +1210,7 @@
         <v>5500</v>
       </c>
       <c r="G13">
-        <v>14.3229166666667</v>
+        <v>14.32</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1203,13 +1224,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -1218,7 +1239,7 @@
         <v>680</v>
       </c>
       <c r="G14">
-        <v>28.3333333333333</v>
+        <v>28.33</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1227,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1235,13 +1256,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1264,13 +1285,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E16">
         <v>600</v>
@@ -1293,13 +1314,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -1308,7 +1329,7 @@
         <v>260</v>
       </c>
       <c r="G17">
-        <v>4.33333333333333</v>
+        <v>4.33</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1322,13 +1343,13 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1337,7 +1358,7 @@
         <v>6200</v>
       </c>
       <c r="G18">
-        <v>103.333333333333</v>
+        <v>103.33</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1346,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1354,13 +1375,13 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1369,7 +1390,7 @@
         <v>50</v>
       </c>
       <c r="G19">
-        <v>8.33333333333333</v>
+        <v>8.33</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1383,13 +1404,13 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1412,13 +1433,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -1427,7 +1448,7 @@
         <v>1100</v>
       </c>
       <c r="G21">
-        <v>91.6666666666667</v>
+        <v>91.67</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1441,13 +1462,13 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1456,7 +1477,7 @@
         <v>920</v>
       </c>
       <c r="G22">
-        <v>76.6666666666667</v>
+        <v>76.67</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1470,13 +1491,13 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1499,13 +1520,13 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -1528,13 +1549,13 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E25">
         <v>1000</v>
@@ -1557,13 +1578,13 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1581,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1589,13 +1610,13 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E27">
         <v>576</v>
@@ -1604,7 +1625,7 @@
         <v>5000</v>
       </c>
       <c r="G27">
-        <v>8.680555555555561</v>
+        <v>8.68</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -1618,13 +1639,13 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E28">
         <v>576</v>
@@ -1633,7 +1654,7 @@
         <v>7000</v>
       </c>
       <c r="G28">
-        <v>12.1527777777778</v>
+        <v>12.15</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -1647,13 +1668,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E29">
         <v>576</v>
@@ -1662,7 +1683,7 @@
         <v>3000</v>
       </c>
       <c r="G29">
-        <v>5.20833333333333</v>
+        <v>5.21</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1676,13 +1697,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E30">
         <v>576</v>
@@ -1691,7 +1712,7 @@
         <v>9500</v>
       </c>
       <c r="G30">
-        <v>16.4930555555556</v>
+        <v>16.49</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -1705,13 +1726,13 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E31">
         <v>576</v>
@@ -1720,7 +1741,7 @@
         <v>6500</v>
       </c>
       <c r="G31">
-        <v>11.2847222222222</v>
+        <v>11.28</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -1734,13 +1755,13 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -1758,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1766,13 +1787,13 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E33">
         <v>24</v>
@@ -1795,13 +1816,13 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E34">
         <v>144</v>
@@ -1810,7 +1831,7 @@
         <v>19000</v>
       </c>
       <c r="G34">
-        <v>131.944444444444</v>
+        <v>131.94</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -1824,13 +1845,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -1839,7 +1860,7 @@
         <v>350</v>
       </c>
       <c r="G35">
-        <v>29.1666666666667</v>
+        <v>29.17</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -1853,13 +1874,13 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -1868,7 +1889,7 @@
         <v>320</v>
       </c>
       <c r="G36">
-        <v>26.6666666666667</v>
+        <v>26.67</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -1882,13 +1903,13 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -1897,7 +1918,7 @@
         <v>170</v>
       </c>
       <c r="G37">
-        <v>14.1666666666667</v>
+        <v>14.17</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -1911,13 +1932,13 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -1940,13 +1961,13 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1969,13 +1990,13 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D40" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -1998,13 +2019,13 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D41" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E41">
         <v>145</v>
@@ -2013,7 +2034,7 @@
         <v>789</v>
       </c>
       <c r="G41">
-        <v>67</v>
+        <v>5.44</v>
       </c>
       <c r="H41">
         <v>12</v>
@@ -2022,10 +2043,10 @@
         <v>16</v>
       </c>
       <c r="J41" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="K41" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2033,13 +2054,13 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E42">
         <v>1</v>
@@ -2048,7 +2069,7 @@
         <v>12.86</v>
       </c>
       <c r="G42">
-        <v>56</v>
+        <v>12.86</v>
       </c>
       <c r="H42">
         <v>12</v>
@@ -2057,10 +2078,74 @@
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="K42" t="s">
-        <v>142</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" t="s">
+        <v>106</v>
+      </c>
+      <c r="D43" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43">
+        <v>500</v>
+      </c>
+      <c r="F43">
+        <v>500</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>20</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="K43" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" t="s">
+        <v>136</v>
+      </c>
+      <c r="E44">
+        <v>20</v>
+      </c>
+      <c r="F44">
+        <v>20</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>13</v>
+      </c>
+      <c r="K44" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
   <si>
     <t>Product Code</t>
   </si>
@@ -169,15 +169,6 @@
     <t>ABT-040</t>
   </si>
   <si>
-    <t>ABT-041</t>
-  </si>
-  <si>
-    <t>ABT-042</t>
-  </si>
-  <si>
-    <t>ABT-043</t>
-  </si>
-  <si>
     <t>Soaps</t>
   </si>
   <si>
@@ -205,15 +196,6 @@
     <t>Checking</t>
   </si>
   <si>
-    <t>soaps</t>
-  </si>
-  <si>
-    <t>Games</t>
-  </si>
-  <si>
-    <t>Pcard</t>
-  </si>
-  <si>
     <t>Turkish Soap</t>
   </si>
   <si>
@@ -334,12 +316,6 @@
     <t>Card1</t>
   </si>
   <si>
-    <t>card2</t>
-  </si>
-  <si>
-    <t>card3</t>
-  </si>
-  <si>
     <t>Carton(48 pcs)</t>
   </si>
   <si>
@@ -421,12 +397,6 @@
     <t>13 packets</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>Confirm pack size</t>
   </si>
   <si>
@@ -448,9 +418,6 @@
     <t>nice product</t>
   </si>
   <si>
-    <t>hi</t>
-  </si>
-  <si>
     <t>Turkish_Soap.jpg</t>
   </si>
   <si>
@@ -458,12 +425,6 @@
   </si>
   <si>
     <t>Card1.png</t>
-  </si>
-  <si>
-    <t>card2.png</t>
-  </si>
-  <si>
-    <t>card3.png</t>
   </si>
 </sst>
 </file>
@@ -821,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -864,13 +825,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -885,10 +846,10 @@
         <v>20</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -896,13 +857,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E3">
         <v>144</v>
@@ -917,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -925,13 +886,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -954,13 +915,13 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -983,13 +944,13 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -1012,13 +973,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -1036,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1044,13 +1005,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1068,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1076,13 +1037,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1105,13 +1066,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1129,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1137,13 +1098,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -1166,13 +1127,13 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1195,13 +1156,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E13">
         <v>384</v>
@@ -1224,13 +1185,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -1248,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1256,13 +1217,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1285,13 +1246,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E16">
         <v>600</v>
@@ -1314,13 +1275,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -1343,13 +1304,13 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1367,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1375,13 +1336,13 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1404,13 +1365,13 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1433,13 +1394,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -1462,13 +1423,13 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1491,13 +1452,13 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1520,13 +1481,13 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -1549,13 +1510,13 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E25">
         <v>1000</v>
@@ -1578,13 +1539,13 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1602,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1610,13 +1571,13 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E27">
         <v>576</v>
@@ -1639,13 +1600,13 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E28">
         <v>576</v>
@@ -1668,13 +1629,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E29">
         <v>576</v>
@@ -1697,13 +1658,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E30">
         <v>576</v>
@@ -1726,13 +1687,13 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E31">
         <v>576</v>
@@ -1755,13 +1716,13 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -1776,10 +1737,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1787,13 +1748,13 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E33">
         <v>24</v>
@@ -1816,13 +1777,13 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E34">
         <v>144</v>
@@ -1845,13 +1806,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -1874,13 +1835,13 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -1903,13 +1864,13 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -1932,13 +1893,13 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
+        <v>96</v>
+      </c>
+      <c r="D38" t="s">
         <v>102</v>
-      </c>
-      <c r="D38" t="s">
-        <v>110</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -1961,13 +1922,13 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1990,13 +1951,13 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -2019,13 +1980,13 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="E41">
         <v>145</v>
@@ -2043,109 +2004,10 @@
         <v>16</v>
       </c>
       <c r="J41" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="K41" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" t="s">
-        <v>106</v>
-      </c>
-      <c r="D42" t="s">
-        <v>135</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="F42">
-        <v>12.86</v>
-      </c>
-      <c r="G42">
-        <v>12.86</v>
-      </c>
-      <c r="H42">
-        <v>12</v>
-      </c>
-      <c r="I42">
-        <v>1</v>
-      </c>
-      <c r="J42" t="s">
-        <v>144</v>
-      </c>
-      <c r="K42" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" t="s">
-        <v>106</v>
-      </c>
-      <c r="D43" t="s">
         <v>136</v>
-      </c>
-      <c r="E43">
-        <v>500</v>
-      </c>
-      <c r="F43">
-        <v>500</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43">
-        <v>20</v>
-      </c>
-      <c r="I43">
-        <v>5</v>
-      </c>
-      <c r="K43" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B44" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" t="s">
-        <v>107</v>
-      </c>
-      <c r="D44" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44">
-        <v>20</v>
-      </c>
-      <c r="F44">
-        <v>20</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>13</v>
-      </c>
-      <c r="K44" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
   <si>
     <t>Product Code</t>
   </si>
@@ -169,6 +169,15 @@
     <t>ABT-040</t>
   </si>
   <si>
+    <t>ABT-041</t>
+  </si>
+  <si>
+    <t>ABT-042</t>
+  </si>
+  <si>
+    <t>ABT-043</t>
+  </si>
+  <si>
     <t>Soaps</t>
   </si>
   <si>
@@ -316,6 +325,12 @@
     <t>Card1</t>
   </si>
   <si>
+    <t>card2</t>
+  </si>
+  <si>
+    <t>card3</t>
+  </si>
+  <si>
     <t>Carton(48 pcs)</t>
   </si>
   <si>
@@ -397,6 +412,12 @@
     <t>13 packets</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>Confirm pack size</t>
   </si>
   <si>
@@ -425,6 +446,9 @@
   </si>
   <si>
     <t>Card1.png</t>
+  </si>
+  <si>
+    <t>card2.png</t>
   </si>
 </sst>
 </file>
@@ -782,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -825,13 +849,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -846,10 +870,10 @@
         <v>20</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -857,13 +881,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E3">
         <v>144</v>
@@ -878,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -886,13 +910,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -915,13 +939,13 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -944,13 +968,13 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -973,13 +997,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -997,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1005,13 +1029,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1029,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1037,13 +1061,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1066,13 +1090,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1090,7 +1114,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1098,13 +1122,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -1127,13 +1151,13 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1156,13 +1180,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E13">
         <v>384</v>
@@ -1185,13 +1209,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -1209,7 +1233,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1217,13 +1241,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1246,13 +1270,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E16">
         <v>600</v>
@@ -1275,13 +1299,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -1304,13 +1328,13 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1328,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1336,13 +1360,13 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1365,13 +1389,13 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1394,13 +1418,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -1423,13 +1447,13 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1452,13 +1476,13 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1481,13 +1505,13 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -1510,13 +1534,13 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E25">
         <v>1000</v>
@@ -1539,13 +1563,13 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1563,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1571,13 +1595,13 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E27">
         <v>576</v>
@@ -1600,13 +1624,13 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E28">
         <v>576</v>
@@ -1629,13 +1653,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E29">
         <v>576</v>
@@ -1658,13 +1682,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E30">
         <v>576</v>
@@ -1687,13 +1711,13 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E31">
         <v>576</v>
@@ -1716,13 +1740,13 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -1737,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1748,13 +1772,13 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E33">
         <v>24</v>
@@ -1777,13 +1801,13 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E34">
         <v>144</v>
@@ -1806,13 +1830,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -1835,13 +1859,13 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -1864,13 +1888,13 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -1893,13 +1917,13 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -1922,13 +1946,13 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1951,13 +1975,13 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -1980,13 +2004,13 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E41">
         <v>145</v>
@@ -2001,13 +2025,103 @@
         <v>12</v>
       </c>
       <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
+        <v>140</v>
+      </c>
+      <c r="K41" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42" t="s">
+        <v>132</v>
+      </c>
+      <c r="E42">
+        <v>11</v>
+      </c>
+      <c r="F42">
+        <v>1600</v>
+      </c>
+      <c r="G42">
+        <v>145.45</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" t="s">
+        <v>133</v>
+      </c>
+      <c r="E43">
+        <v>15</v>
+      </c>
+      <c r="F43">
+        <v>688.92</v>
+      </c>
+      <c r="G43">
+        <v>45.93</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44">
+        <v>12</v>
+      </c>
+      <c r="F44">
+        <v>150</v>
+      </c>
+      <c r="G44">
+        <v>12.5</v>
+      </c>
+      <c r="H44">
         <v>16</v>
       </c>
-      <c r="J41" t="s">
-        <v>133</v>
-      </c>
-      <c r="K41" t="s">
-        <v>136</v>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="K44" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="144">
   <si>
     <t>Product Code</t>
   </si>
@@ -173,9 +173,6 @@
   </si>
   <si>
     <t>ABT-042</t>
-  </si>
-  <si>
-    <t>ABT-043</t>
   </si>
   <si>
     <t>Soaps</t>
@@ -806,7 +803,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -849,13 +846,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -873,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -881,13 +878,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E3">
         <v>144</v>
@@ -910,13 +907,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -939,13 +936,13 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -968,13 +965,13 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -997,13 +994,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -1021,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1029,13 +1026,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1053,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1061,13 +1058,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1090,13 +1087,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1114,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1122,13 +1119,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -1151,13 +1148,13 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1180,13 +1177,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E13">
         <v>384</v>
@@ -1209,13 +1206,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -1233,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1241,13 +1238,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1270,13 +1267,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E16">
         <v>600</v>
@@ -1299,13 +1296,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -1328,13 +1325,13 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1352,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1360,13 +1357,13 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1389,13 +1386,13 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1418,13 +1415,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -1447,13 +1444,13 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1476,13 +1473,13 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1505,13 +1502,13 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -1534,13 +1531,13 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E25">
         <v>1000</v>
@@ -1563,13 +1560,13 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1587,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1595,13 +1592,13 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E27">
         <v>576</v>
@@ -1624,13 +1621,13 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E28">
         <v>576</v>
@@ -1653,13 +1650,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E29">
         <v>576</v>
@@ -1682,13 +1679,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E30">
         <v>576</v>
@@ -1711,13 +1708,13 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E31">
         <v>576</v>
@@ -1740,13 +1737,13 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -1764,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1772,13 +1769,13 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33">
         <v>24</v>
@@ -1801,13 +1798,13 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E34">
         <v>144</v>
@@ -1830,13 +1827,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -1859,13 +1856,13 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -1888,13 +1885,13 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -1917,13 +1914,13 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -1946,13 +1943,13 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1975,13 +1972,13 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -2004,13 +2001,13 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E41">
         <v>145</v>
@@ -2028,10 +2025,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2039,13 +2036,13 @@
         <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E42">
         <v>11</v>
@@ -2060,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K42" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2071,13 +2068,13 @@
         <v>52</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D43" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E43">
         <v>15</v>
@@ -2093,35 +2090,6 @@
       </c>
       <c r="I43">
         <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" t="s">
-        <v>53</v>
-      </c>
-      <c r="B44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
-      </c>
-      <c r="E44">
-        <v>12</v>
-      </c>
-      <c r="F44">
-        <v>150</v>
-      </c>
-      <c r="G44">
-        <v>12.5</v>
-      </c>
-      <c r="H44">
-        <v>16</v>
-      </c>
-      <c r="I44">
-        <v>5</v>
-      </c>
-      <c r="K44" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
   <si>
     <t>Product Code</t>
   </si>
@@ -169,12 +169,6 @@
     <t>ABT-040</t>
   </si>
   <si>
-    <t>ABT-041</t>
-  </si>
-  <si>
-    <t>ABT-042</t>
-  </si>
-  <si>
     <t>Soaps</t>
   </si>
   <si>
@@ -322,12 +316,6 @@
     <t>Card1</t>
   </si>
   <si>
-    <t>card2</t>
-  </si>
-  <si>
-    <t>card3</t>
-  </si>
-  <si>
     <t>Carton(48 pcs)</t>
   </si>
   <si>
@@ -409,12 +397,6 @@
     <t>13 packets</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>Confirm pack size</t>
   </si>
   <si>
@@ -443,9 +425,6 @@
   </si>
   <si>
     <t>Card1.png</t>
-  </si>
-  <si>
-    <t>card2.png</t>
   </si>
 </sst>
 </file>
@@ -803,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -846,13 +825,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -870,7 +849,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -878,13 +857,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E3">
         <v>144</v>
@@ -907,13 +886,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -936,13 +915,13 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -965,13 +944,13 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -994,13 +973,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -1018,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1026,13 +1005,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1050,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1058,13 +1037,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1087,13 +1066,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1111,7 +1090,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1119,13 +1098,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -1148,13 +1127,13 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1177,13 +1156,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E13">
         <v>384</v>
@@ -1206,13 +1185,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -1230,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1238,13 +1217,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1267,13 +1246,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E16">
         <v>600</v>
@@ -1296,13 +1275,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -1325,13 +1304,13 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1349,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1357,13 +1336,13 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1386,13 +1365,13 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1415,13 +1394,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -1444,13 +1423,13 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1473,13 +1452,13 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1502,13 +1481,13 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -1531,13 +1510,13 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E25">
         <v>1000</v>
@@ -1560,13 +1539,13 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1584,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1592,13 +1571,13 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E27">
         <v>576</v>
@@ -1621,13 +1600,13 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E28">
         <v>576</v>
@@ -1650,13 +1629,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E29">
         <v>576</v>
@@ -1679,13 +1658,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E30">
         <v>576</v>
@@ -1708,13 +1687,13 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E31">
         <v>576</v>
@@ -1737,13 +1716,13 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -1761,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1769,13 +1748,13 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E33">
         <v>24</v>
@@ -1798,13 +1777,13 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E34">
         <v>144</v>
@@ -1827,13 +1806,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -1856,13 +1835,13 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C36" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -1885,13 +1864,13 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -1914,13 +1893,13 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -1943,13 +1922,13 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1972,13 +1951,13 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -2001,13 +1980,13 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E41">
         <v>145</v>
@@ -2025,71 +2004,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="K41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42">
-        <v>11</v>
-      </c>
-      <c r="F42">
-        <v>1600</v>
-      </c>
-      <c r="G42">
-        <v>145.45</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-      <c r="I42">
-        <v>7</v>
-      </c>
-      <c r="K42" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" t="s">
-        <v>61</v>
-      </c>
-      <c r="C43" t="s">
-        <v>103</v>
-      </c>
-      <c r="D43" t="s">
-        <v>132</v>
-      </c>
-      <c r="E43">
-        <v>15</v>
-      </c>
-      <c r="F43">
-        <v>688.92</v>
-      </c>
-      <c r="G43">
-        <v>45.93</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-      <c r="I43">
-        <v>4</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="141">
   <si>
     <t>Product Code</t>
   </si>
@@ -169,6 +169,9 @@
     <t>ABT-040</t>
   </si>
   <si>
+    <t>ABT-041</t>
+  </si>
+  <si>
     <t>Soaps</t>
   </si>
   <si>
@@ -316,6 +319,9 @@
     <t>Card1</t>
   </si>
   <si>
+    <t>card2</t>
+  </si>
+  <si>
     <t>Carton(48 pcs)</t>
   </si>
   <si>
@@ -397,6 +403,9 @@
     <t>13 packets</t>
   </si>
   <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>Confirm pack size</t>
   </si>
   <si>
@@ -425,6 +434,9 @@
   </si>
   <si>
     <t>Card1.png</t>
+  </si>
+  <si>
+    <t>card2.png</t>
   </si>
 </sst>
 </file>
@@ -782,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -825,13 +837,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2">
         <v>48</v>
@@ -849,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -857,13 +869,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E3">
         <v>144</v>
@@ -886,13 +898,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E4">
         <v>12</v>
@@ -915,13 +927,13 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E5">
         <v>12</v>
@@ -944,13 +956,13 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E6">
         <v>12</v>
@@ -973,13 +985,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E7">
         <v>12</v>
@@ -997,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1005,13 +1017,13 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8">
         <v>12</v>
@@ -1029,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1037,13 +1049,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -1066,13 +1078,13 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E10">
         <v>10</v>
@@ -1090,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1098,13 +1110,13 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E11">
         <v>12</v>
@@ -1127,13 +1139,13 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E12">
         <v>20</v>
@@ -1156,13 +1168,13 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E13">
         <v>384</v>
@@ -1185,13 +1197,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E14">
         <v>24</v>
@@ -1209,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1217,13 +1229,13 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1246,13 +1258,13 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E16">
         <v>600</v>
@@ -1275,13 +1287,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E17">
         <v>60</v>
@@ -1304,13 +1316,13 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E18">
         <v>60</v>
@@ -1328,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1336,13 +1348,13 @@
         <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E19">
         <v>6</v>
@@ -1365,13 +1377,13 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E20">
         <v>12</v>
@@ -1394,13 +1406,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E21">
         <v>12</v>
@@ -1423,13 +1435,13 @@
         <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E22">
         <v>12</v>
@@ -1452,13 +1464,13 @@
         <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -1481,13 +1493,13 @@
         <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E24">
         <v>12</v>
@@ -1510,13 +1522,13 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E25">
         <v>1000</v>
@@ -1539,13 +1551,13 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E26">
         <v>12</v>
@@ -1563,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="J26" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1571,13 +1583,13 @@
         <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E27">
         <v>576</v>
@@ -1600,13 +1612,13 @@
         <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E28">
         <v>576</v>
@@ -1629,13 +1641,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E29">
         <v>576</v>
@@ -1658,13 +1670,13 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E30">
         <v>576</v>
@@ -1687,13 +1699,13 @@
         <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E31">
         <v>576</v>
@@ -1716,13 +1728,13 @@
         <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E32">
         <v>100</v>
@@ -1740,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1748,13 +1760,13 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E33">
         <v>24</v>
@@ -1777,13 +1789,13 @@
         <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E34">
         <v>144</v>
@@ -1806,13 +1818,13 @@
         <v>44</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E35">
         <v>12</v>
@@ -1835,13 +1847,13 @@
         <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E36">
         <v>12</v>
@@ -1864,13 +1876,13 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D37" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E37">
         <v>12</v>
@@ -1893,13 +1905,13 @@
         <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E38">
         <v>12</v>
@@ -1922,13 +1934,13 @@
         <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E39">
         <v>12</v>
@@ -1951,13 +1963,13 @@
         <v>49</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E40">
         <v>120</v>
@@ -1980,13 +1992,13 @@
         <v>50</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E41">
         <v>145</v>
@@ -2004,10 +2016,42 @@
         <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K41" t="s">
-        <v>136</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42" t="s">
+        <v>101</v>
+      </c>
+      <c r="D42" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42">
+        <v>67</v>
+      </c>
+      <c r="F42">
+        <v>1670</v>
+      </c>
+      <c r="G42">
+        <v>24.93</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>13</v>
+      </c>
+      <c r="K42" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="K42" t="s">
         <v>140</v>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K42" t="s">
         <v>140</v>

--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -2048,7 +2048,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K42" t="s">
         <v>140</v>
